--- a/results/Int All Data -0.6/Rando_5_permute.xlsx
+++ b/results/Int All Data -0.6/Rando_5_permute.xlsx
@@ -440,1397 +440,1397 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7993374094419683</v>
+        <v>0.7998336660481644</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8001725987515451</v>
+        <v>0.7963570541644729</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7982009466182751</v>
+        <v>0.7983287062977427</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7999843028052225</v>
+        <v>0.7983287062977427</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8147864759164205</v>
+        <v>0.7980503098612171</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.812611745725154</v>
+        <v>0.7833153601626315</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.81352225341326</v>
+        <v>0.7972365898090714</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8154939055465299</v>
+        <v>0.8008261792605565</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8172396025442126</v>
+        <v>0.8065528397140436</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8172396025442126</v>
+        <v>0.8065904989033081</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8184285066688441</v>
+        <v>0.8049725615850929</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8250280156211725</v>
+        <v>0.8090436255311002</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8287453647521251</v>
+        <v>0.8101572112772026</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8222964925568548</v>
+        <v>0.8097133959719449</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8260434059111552</v>
+        <v>0.8097133959719449</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8260434059111552</v>
+        <v>0.8401677136155918</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8218822414749449</v>
+        <v>0.8352843374375984</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8222359562899997</v>
+        <v>0.8382565977491772</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8219199006642095</v>
+        <v>0.8282033539907478</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8349601868458916</v>
+        <v>0.8255471493049592</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8457585194236947</v>
+        <v>0.8232070002449607</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8427795719663587</v>
+        <v>0.8232070002449607</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8460154466027892</v>
+        <v>0.8217396996838036</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8519828443035373</v>
+        <v>0.8217396996838036</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8500917898743943</v>
+        <v>0.8221687328773873</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.851581967513142</v>
+        <v>0.8208520690732883</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.84559978770072</v>
+        <v>0.8186396796927573</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8458781841372456</v>
+        <v>0.8204754771806431</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8458781841372456</v>
+        <v>0.8186921209936958</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8407083165568098</v>
+        <v>0.8162537764775777</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8343495448517424</v>
+        <v>0.8177210770387349</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8263270816732787</v>
+        <v>0.8177210770387349</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8301869725953728</v>
+        <v>0.8127771645938862</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8293141240965314</v>
+        <v>0.8118666569057802</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8395408816896095</v>
+        <v>0.8030547585729209</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8433564262766817</v>
+        <v>0.8036868698245011</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8430403706508915</v>
+        <v>0.8089697149727306</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8392100439521454</v>
+        <v>0.7911428402490153</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8370958500277341</v>
+        <v>0.7843550353503642</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8428077283695472</v>
+        <v>0.7821049867805687</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8423181589091082</v>
+        <v>0.7894495845522709</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8353272759524608</v>
+        <v>0.80417643928494</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8366815989458243</v>
+        <v>0.80417643928494</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.859866637196298</v>
+        <v>0.7780758054843042</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8605364076371429</v>
+        <v>0.7932288777702381</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8644582426462514</v>
+        <v>0.7822045900568477</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.866949028463308</v>
+        <v>0.782671282439696</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8690860994653099</v>
+        <v>0.7832738294679285</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8690860994653099</v>
+        <v>0.7887287806306471</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8694021550911001</v>
+        <v>0.798729583088138</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8735108782263719</v>
+        <v>0.8053600640839736</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8824357541270248</v>
+        <v>0.8093477146855352</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8777998023420497</v>
+        <v>0.8093477146855352</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8765880211398275</v>
+        <v>0.8093477146855352</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8778145844537235</v>
+        <v>0.8135908846460318</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8701162718669666</v>
+        <v>0.8126050585793969</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8692434233681252</v>
+        <v>0.8209354824177341</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8721861194563563</v>
+        <v>0.8212891972327887</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8757757089078413</v>
+        <v>0.8240731615980448</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8516949450809356</v>
+        <v>0.8271436173657433</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8384353909094237</v>
+        <v>0.807203956537776</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8387514465352138</v>
+        <v>0.8047131707207195</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8394212169760586</v>
+        <v>0.7998069174651353</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8421756171179668</v>
+        <v>0.7985803541512393</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.822512944906366</v>
+        <v>0.792606269304734</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.822512944906366</v>
+        <v>0.7953458873349684</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8285637559515597</v>
+        <v>0.7895896626581334</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8280069630785085</v>
+        <v>0.8005534141046686</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8379553242350609</v>
+        <v>0.8007941513519297</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.806542281062848</v>
+        <v>0.8024536193648479</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7971669027111801</v>
+        <v>0.7995485824658815</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8091622343795315</v>
+        <v>0.7998646380916716</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8143912304066629</v>
+        <v>0.7999022972809362</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8137739012667566</v>
+        <v>0.8124100754873169</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8132171083937054</v>
+        <v>0.7801319268271394</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8242118318837479</v>
+        <v>0.7785516486981887</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.824527887509538</v>
+        <v>0.7581882340022357</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8203290638840632</v>
+        <v>0.756607955873285</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8171093791794661</v>
+        <v>0.7659604571473622</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8171470383687306</v>
+        <v>0.7742155626071703</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.818200087847978</v>
+        <v>0.7710550063492689</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.8180508589110793</v>
+        <v>0.7707766099127433</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7761984773017157</v>
+        <v>0.7803564741425671</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7743250206245653</v>
+        <v>0.7148347641478887</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.777056543688883</v>
+        <v>0.7145187085220985</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7692009071993108</v>
+        <v>0.7109143369589395</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7696675995821589</v>
+        <v>0.7086266291998795</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7666710543728301</v>
+        <v>0.7086266291998795</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7302961490487359</v>
+        <v>0.7024709355528087</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7302961490487359</v>
+        <v>0.7040512136817594</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7236684836932191</v>
+        <v>0.7035845212989111</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7215704797006411</v>
+        <v>0.7053678774858585</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.721254424074851</v>
+        <v>0.7064061448534318</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.725499001855507</v>
+        <v>0.7058493519803806</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7231359757179179</v>
+        <v>0.7058493519803806</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7225415236556021</v>
+        <v>0.7061277484169062</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7222039987723808</v>
+        <v>0.7183638173325186</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7579936028651956</v>
+        <v>0.6407176081698619</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7546380635152143</v>
+        <v>0.663203311756143</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.7609362989534265</v>
+        <v>0.6489054902170577</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.6585610247804505</v>
+        <v>0.6484240157225356</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6574917853693698</v>
+        <v>0.6609761402639381</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6349912996714148</v>
+        <v>0.654843323694458</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6477169380474661</v>
+        <v>0.6511865108303605</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6470848267958857</v>
+        <v>0.6594563984018426</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6470848267958857</v>
+        <v>0.6610285815648766</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.6334191165083808</v>
+        <v>0.5901473002232802</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.6314474643751109</v>
+        <v>0.592968923777801</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6293251754847828</v>
+        <v>0.5858274040640952</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.615861135435115</v>
+        <v>0.5829976855436579</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6136635281662579</v>
+        <v>0.5818087814190264</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.6083739958722713</v>
+        <v>0.6052345569167612</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.6366307062470612</v>
+        <v>0.5826210936510127</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5781885718790739</v>
+        <v>0.5806885085271667</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5686168026151668</v>
+        <v>0.5806885085271667</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5738162344189504</v>
+        <v>0.5550894106583248</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5737409160404213</v>
+        <v>0.5550894106583248</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5699186843075918</v>
+        <v>0.5192987507003906</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5508465926528682</v>
+        <v>0.5262586616135309</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5553843489817237</v>
+        <v>0.5127879344181057</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5311983505979012</v>
+        <v>0.4852643463913346</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5810221619049496</v>
+        <v>0.4957698523759781</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5811499215844171</v>
+        <v>0.4694710678879038</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.59435844227515</v>
+        <v>0.4757636720454782</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.578967096427234</v>
+        <v>0.4790291109052566</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5806751342356522</v>
+        <v>0.4954235286167604</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5818263791710192</v>
+        <v>0.4954235286167604</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5719452414270791</v>
+        <v>0.4841694142623445</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5707711194141215</v>
+        <v>0.4803552774954316</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5738039159925554</v>
+        <v>0.479911462190174</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5615301878876785</v>
+        <v>0.4573842279091899</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.55334899298624</v>
+        <v>0.4573842279091899</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5349290740203684</v>
+        <v>0.4574218870984544</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5346883367731072</v>
+        <v>0.4664731148584155</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5318667132185866</v>
+        <v>0.4515379027421521</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5317308585732025</v>
+        <v>0.5091483673509611</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5273518339673217</v>
+        <v>0.476331375524765</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4960436733969856</v>
+        <v>0.4769634867763453</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4960436733969856</v>
+        <v>0.4766850903398196</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4994058998927241</v>
+        <v>0.4766850903398196</v>
       </c>
     </row>
     <row r="142">
@@ -1840,147 +1840,147 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5026956236502524</v>
+        <v>0.4733753051450196</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5037810529931664</v>
+        <v>0.4723465405635222</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5037810529931664</v>
+        <v>0.4666937906684049</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4984524536897559</v>
+        <v>0.4697790285477772</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4494856529047553</v>
+        <v>0.4862807925464369</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4499819095109514</v>
+        <v>0.4862807925464369</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4508251937864449</v>
+        <v>0.4925909944560042</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4933674072739252</v>
+        <v>0.497685543657911</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5036891927277641</v>
+        <v>0.4988959170399736</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5043132090134278</v>
+        <v>0.4988959170399736</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5041101309554312</v>
+        <v>0.4991743134764992</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.504524382037341</v>
+        <v>0.4991514363989086</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5027558079620678</v>
+        <v>0.5010396751877328</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5003632176011308</v>
+        <v>0.4999260894416304</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5029212268307998</v>
+        <v>0.4969995832852328</v>
       </c>
     </row>
   </sheetData>
